--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20241.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -73,79 +73,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>AZPIRI</t>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>JANETH</t>
-  </si>
-  <si>
-    <t>ALEX TADEO</t>
-  </si>
-  <si>
-    <t>ANGEL EDUC</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ANIELA SAMANTA</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
+    <t>ARIADNA JARETZI</t>
   </si>
   <si>
     <t>AXEL</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
   </si>
 </sst>
 </file>
@@ -689,16 +629,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>94.44</v>
+      </c>
+      <c r="H2">
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -712,16 +655,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88.89</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -735,16 +681,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>97.3</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -758,16 +707,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>94.59</v>
+      </c>
+      <c r="H5">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -823,16 +775,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>63.89</v>
+        <v>94.44</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -849,16 +801,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>80.56</v>
+        <v>88.89</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -875,16 +827,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>89.19</v>
+        <v>97.3</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -901,13 +853,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>91.89</v>
+        <v>94.59</v>
       </c>
       <c r="H5">
         <v>8.6</v>
@@ -920,7 +872,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -952,19 +904,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920079</v>
+        <v>23330051920111</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -975,185 +927,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920086</v>
+        <v>23330051920144</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920234</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920099</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920104</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920261</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920118</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920144</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920150</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20241.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="35">
   <si>
     <t>Mat</t>
   </si>
@@ -73,13 +73,49 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>TEXOCO</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
     <t>CRUZ</t>
+  </si>
+  <si>
+    <t>JAIRO</t>
+  </si>
+  <si>
+    <t>MELANY</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
   </si>
   <si>
     <t>ARIADNA JARETZI</t>
@@ -872,7 +908,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -904,19 +940,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920111</v>
+        <v>23330051920230</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -927,25 +963,186 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920144</v>
+        <v>23330051920230</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>23330051920105</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>23330051920105</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>23330051920113</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920404</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
         <v>11</v>
       </c>
-      <c r="G3">
-        <v>2</v>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920404</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920111</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>23330051920144</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20241.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20241.xlsx
@@ -73,52 +73,52 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>RIVERA</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
   </si>
   <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
     <t>SANTOS</t>
   </si>
   <si>
-    <t>OLMOS</t>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>BAEZ</t>
   </si>
   <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
+    <t>MELANY</t>
   </si>
   <si>
     <t>JAIRO</t>
   </si>
   <si>
-    <t>MELANY</t>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>ARIADNA JARETZI</t>
   </si>
   <si>
     <t>YAMILETH</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>ARIADNA JARETZI</t>
   </si>
   <si>
     <t>AXEL</t>
@@ -940,7 +940,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920230</v>
+        <v>23330051920105</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -958,12 +958,12 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920230</v>
+        <v>23330051920105</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
@@ -981,12 +981,12 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920105</v>
+        <v>23330051920230</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920105</v>
+        <v>23330051920230</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
@@ -1032,7 +1032,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920113</v>
+        <v>22330051920404</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
@@ -1044,10 +1044,10 @@
         <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1058,16 +1058,16 @@
         <v>22330051920404</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920404</v>
+        <v>23330051920111</v>
       </c>
       <c r="B8" t="s">
         <v>21</v>
@@ -1093,15 +1093,15 @@
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920111</v>
+        <v>23330051920113</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20241.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="18">
   <si>
     <t>Mat</t>
   </si>
@@ -71,57 +71,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>MELANY</t>
-  </si>
-  <si>
-    <t>JAIRO</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>ARIADNA JARETZI</t>
-  </si>
-  <si>
-    <t>YAMILETH</t>
-  </si>
-  <si>
-    <t>AXEL</t>
   </si>
 </sst>
 </file>
@@ -811,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -837,16 +786,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>88.89</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -863,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>8.699999999999999</v>
@@ -889,16 +838,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -908,7 +857,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -938,213 +887,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920105</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920105</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920230</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920230</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920404</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920404</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920111</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920113</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920144</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
